--- a/tests/data_golden/follow.template.xlsx
+++ b/tests/data_golden/follow.template.xlsx
@@ -31,6 +31,8 @@
     <sheet name="follow-rc-merged" sheetId="22" r:id="rId25"/>
     <sheet name="follow-cr-merged" sheetId="23" r:id="rId26"/>
     <sheet name="follow-cc-merged" sheetId="24" r:id="rId27"/>
+    <sheet name="follow-r-cond-format-inside" sheetId="25" r:id="rId28"/>
+    <sheet name="follow-r-defined-name-inside" sheetId="26" r:id="rId29"/>
   </sheets>
   <definedNames>
     <definedName name="FolRName">'follow-r-defined-name'!$B$3:$E$4</definedName>
@@ -39,13 +41,14 @@
     <definedName localSheetId="7" name="_xlnm.Print_Area">'follow-c-print-area'!$B$2:$F$4</definedName>
     <definedName hidden="true" localSheetId="8" name="_xlnm._FilterDatabase">'follow-r-filter'!$B$2:$E$4</definedName>
     <definedName hidden="true" localSheetId="9" name="_xlnm._FilterDatabase">'follow-c-filter'!$B$2:$D$3</definedName>
+    <definedName name="FolRInside">'follow-r-defined-name-inside'!$B$2:$C$3</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="36">
   <si>
     <t>Name</t>
   </si>
@@ -193,11 +196,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1598,6 +1608,88 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="3"/>
+    <col customWidth="true" max="5" min="2" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B3:C3">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" operator="between" sqref="B4" type="textLength">
+      <formula1>1</formula1>
+      <formula2>20</formula2>
+    </dataValidation>
+  </dataValidations>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="3"/>
+    <col customWidth="true" max="5" min="2" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
